--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/parametre.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/parametre.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75,71</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>22,71</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>540</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
